--- a/outputs/tabel/tabel_17_perbandingan_metrik_evaluasi_akhir_lstm_vs_gru.xlsx
+++ b/outputs/tabel/tabel_17_perbandingan_metrik_evaluasi_akhir_lstm_vs_gru.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>79.56</t>
+          <t>143.72</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>150.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.2874</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.3008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
